--- a/artfynd/A 1828-2024 artfynd.xlsx
+++ b/artfynd/A 1828-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1828-2024 artfynd.xlsx
+++ b/artfynd/A 1828-2024 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119537353</v>
+        <v>119537499</v>
       </c>
       <c r="B13" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119537499</v>
+        <v>119537291</v>
       </c>
       <c r="B14" t="n">
-        <v>91834</v>
+        <v>89275</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>6286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687539</v>
+        <v>687488</v>
       </c>
       <c r="R14" t="n">
-        <v>7128579</v>
+        <v>7128555</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119537463</v>
+        <v>119537353</v>
       </c>
       <c r="B16" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687555</v>
+        <v>687539</v>
       </c>
       <c r="R16" t="n">
-        <v>7128550</v>
+        <v>7128579</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119537291</v>
+        <v>119537463</v>
       </c>
       <c r="B17" t="n">
-        <v>89275</v>
+        <v>78171</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6286</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>687488</v>
+        <v>687555</v>
       </c>
       <c r="R17" t="n">
-        <v>7128555</v>
+        <v>7128550</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 1828-2024 artfynd.xlsx
+++ b/artfynd/A 1828-2024 artfynd.xlsx
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119537499</v>
+        <v>119537320</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
+        <v>91883</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687539</v>
+        <v>687486</v>
       </c>
       <c r="R13" t="n">
-        <v>7128579</v>
+        <v>7128574</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119537291</v>
+        <v>119537353</v>
       </c>
       <c r="B14" t="n">
-        <v>89275</v>
+        <v>91856</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6286</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687488</v>
+        <v>687539</v>
       </c>
       <c r="R14" t="n">
-        <v>7128555</v>
+        <v>7128579</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119537320</v>
+        <v>119537499</v>
       </c>
       <c r="B15" t="n">
-        <v>91883</v>
+        <v>91834</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>687486</v>
+        <v>687539</v>
       </c>
       <c r="R15" t="n">
-        <v>7128574</v>
+        <v>7128579</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119537353</v>
+        <v>119537291</v>
       </c>
       <c r="B16" t="n">
-        <v>91856</v>
+        <v>89275</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>6286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>687539</v>
+        <v>687488</v>
       </c>
       <c r="R16" t="n">
-        <v>7128579</v>
+        <v>7128555</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
